--- a/results/results_mortality.xlsx
+++ b/results/results_mortality.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
